--- a/Data/Home/Kitchen.MicrowaveOven001.xlsx
+++ b/Data/Home/Kitchen.MicrowaveOven001.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H229"/>
+  <dimension ref="A1:I211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -469,6 +469,11 @@
           <t>actionSource</t>
         </is>
       </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>violationLabel</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -487,7 +492,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>1709252725</v>
+        <v>1711842487</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -497,7 +502,7 @@
       <c r="F2" t="inlineStr"/>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -505,6 +510,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -523,7 +529,7 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>1709271700</v>
+        <v>1711842587</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -533,7 +539,7 @@
       <c r="F3" t="inlineStr"/>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -541,6 +547,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -559,7 +566,7 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>1709271870</v>
+        <v>1711845163</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -577,6 +584,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -595,7 +603,7 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>1709272430</v>
+        <v>1711859277</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -605,7 +613,7 @@
       <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -613,6 +621,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -631,7 +640,7 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>1709273635</v>
+        <v>1711859412</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -649,6 +658,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -667,7 +677,7 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>1709275815</v>
+        <v>1711861566</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -685,6 +695,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -703,7 +714,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>1709244647</v>
+        <v>1711867351</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -713,7 +724,7 @@
       <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -721,6 +732,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -739,7 +751,7 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>1709244703</v>
+        <v>1711872947</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -757,6 +769,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -775,7 +788,7 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>1709246796</v>
+        <v>1711879704</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -793,6 +806,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -811,7 +825,7 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>1709259402</v>
+        <v>1711880068</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -821,7 +835,7 @@
       <c r="F11" t="inlineStr"/>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -829,6 +843,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -847,7 +862,7 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>1709262493</v>
+        <v>1711880282</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -865,6 +880,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -883,7 +899,7 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>1709271854</v>
+        <v>1711883575</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -901,6 +917,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -919,7 +936,7 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>1709332825</v>
+        <v>1711885632</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -937,6 +954,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -955,7 +973,7 @@
         </is>
       </c>
       <c r="D15" t="n">
-        <v>1709344544</v>
+        <v>1711930066</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -973,6 +991,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -991,7 +1010,7 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>1709346005</v>
+        <v>1711945393</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -1009,6 +1028,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1027,7 +1047,7 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>1709346129</v>
+        <v>1711945469</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -1045,6 +1065,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1063,7 +1084,7 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>1709347582</v>
+        <v>1711947873</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -1081,6 +1102,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1099,7 +1121,7 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>1709356274</v>
+        <v>1711956603</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -1109,7 +1131,7 @@
       <c r="F19" t="inlineStr"/>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
@@ -1117,6 +1139,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -1135,7 +1158,7 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>1709417216</v>
+        <v>1711956683</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -1145,7 +1168,7 @@
       <c r="F20" t="inlineStr"/>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
@@ -1153,6 +1176,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -1171,7 +1195,7 @@
         </is>
       </c>
       <c r="D21" t="n">
-        <v>1709417342</v>
+        <v>1711959067</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -1189,6 +1213,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -1207,7 +1232,7 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>1709419507</v>
+        <v>1711965077</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -1225,6 +1250,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -1243,7 +1269,7 @@
         </is>
       </c>
       <c r="D23" t="n">
-        <v>1709438511</v>
+        <v>1712015262</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -1261,6 +1287,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -1279,7 +1306,7 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>1709438699</v>
+        <v>1712015358</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -1297,6 +1324,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -1315,7 +1343,7 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>1709441491</v>
+        <v>1712018483</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -1333,6 +1361,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -1351,7 +1380,7 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>1709443150</v>
+        <v>1712040472</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -1369,6 +1398,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
@@ -1387,7 +1417,7 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>1709443189</v>
+        <v>1712042904</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -1405,6 +1435,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
@@ -1423,7 +1454,7 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>1709505468</v>
+        <v>1712044687</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
@@ -1441,6 +1472,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
@@ -1459,7 +1491,7 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>1709514541</v>
+        <v>1712059154</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
@@ -1477,6 +1509,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
@@ -1495,7 +1528,7 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>1709514608</v>
+        <v>1712059271</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
@@ -1513,6 +1546,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
@@ -1531,7 +1565,7 @@
         </is>
       </c>
       <c r="D31" t="n">
-        <v>1709517470</v>
+        <v>1712061362</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
@@ -1549,6 +1583,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
@@ -1567,7 +1602,7 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>1709528351</v>
+        <v>1712101664</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
@@ -1577,7 +1612,7 @@
       <c r="F32" t="inlineStr"/>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
@@ -1585,6 +1620,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
@@ -1603,7 +1639,7 @@
         </is>
       </c>
       <c r="D33" t="n">
-        <v>1709530360</v>
+        <v>1712101807</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
@@ -1621,6 +1657,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
@@ -1639,7 +1676,7 @@
         </is>
       </c>
       <c r="D34" t="n">
-        <v>1709538805</v>
+        <v>1712105345</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
@@ -1649,7 +1686,7 @@
       <c r="F34" t="inlineStr"/>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
@@ -1657,6 +1694,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
@@ -1675,7 +1713,7 @@
         </is>
       </c>
       <c r="D35" t="n">
-        <v>1709539005</v>
+        <v>1712125733</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
@@ -1693,6 +1731,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
@@ -1711,7 +1750,7 @@
         </is>
       </c>
       <c r="D36" t="n">
-        <v>1709541929</v>
+        <v>1712128357</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
@@ -1721,7 +1760,7 @@
       <c r="F36" t="inlineStr"/>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
@@ -1729,6 +1768,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
@@ -1747,7 +1787,7 @@
         </is>
       </c>
       <c r="D37" t="n">
-        <v>1709543401</v>
+        <v>1712128488</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
@@ -1757,7 +1797,7 @@
       <c r="F37" t="inlineStr"/>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
@@ -1765,6 +1805,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
@@ -1783,7 +1824,7 @@
         </is>
       </c>
       <c r="D38" t="n">
-        <v>1709543647</v>
+        <v>1712131419</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
@@ -1801,6 +1842,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
@@ -1819,7 +1861,7 @@
         </is>
       </c>
       <c r="D39" t="n">
-        <v>1709546595</v>
+        <v>1712132194</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
@@ -1837,6 +1879,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
@@ -1855,7 +1898,7 @@
         </is>
       </c>
       <c r="D40" t="n">
-        <v>1709589093</v>
+        <v>1712148054</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
@@ -1873,6 +1916,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
@@ -1891,7 +1935,7 @@
         </is>
       </c>
       <c r="D41" t="n">
-        <v>1709589308</v>
+        <v>1712148152</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
@@ -1909,6 +1953,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
@@ -1927,7 +1972,7 @@
         </is>
       </c>
       <c r="D42" t="n">
-        <v>1709592419</v>
+        <v>1712152797</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
@@ -1945,6 +1990,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
@@ -1963,7 +2009,7 @@
         </is>
       </c>
       <c r="D43" t="n">
-        <v>1709607312</v>
+        <v>1712192057</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
@@ -1981,6 +2027,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
@@ -1999,7 +2046,7 @@
         </is>
       </c>
       <c r="D44" t="n">
-        <v>1709611351</v>
+        <v>1712202543</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
@@ -2009,7 +2056,7 @@
       <c r="F44" t="inlineStr"/>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
@@ -2017,6 +2064,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
@@ -2035,7 +2083,7 @@
         </is>
       </c>
       <c r="D45" t="n">
-        <v>1709616823</v>
+        <v>1712202730</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
@@ -2053,6 +2101,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
@@ -2071,7 +2120,7 @@
         </is>
       </c>
       <c r="D46" t="n">
-        <v>1709619254</v>
+        <v>1712205857</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
@@ -2089,6 +2138,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
@@ -2107,7 +2157,7 @@
         </is>
       </c>
       <c r="D47" t="n">
-        <v>1709688884</v>
+        <v>1712206171</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
@@ -2125,6 +2175,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2143,7 +2194,7 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>1709689083</v>
+        <v>1712206242</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
@@ -2161,6 +2212,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2179,7 +2231,7 @@
         </is>
       </c>
       <c r="D49" t="n">
-        <v>1709690121</v>
+        <v>1712209613</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
@@ -2197,6 +2249,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -2215,7 +2268,7 @@
         </is>
       </c>
       <c r="D50" t="n">
-        <v>1709691175</v>
+        <v>1712209707</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
@@ -2225,7 +2278,7 @@
       <c r="F50" t="inlineStr"/>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
@@ -2233,6 +2286,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
@@ -2251,7 +2305,7 @@
         </is>
       </c>
       <c r="D51" t="n">
-        <v>1709697791</v>
+        <v>1712209830</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
@@ -2261,7 +2315,7 @@
       <c r="F51" t="inlineStr"/>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
@@ -2269,6 +2323,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
@@ -2287,7 +2342,7 @@
         </is>
       </c>
       <c r="D52" t="n">
-        <v>1709697889</v>
+        <v>1712212318</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
@@ -2305,6 +2360,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
@@ -2323,7 +2379,7 @@
         </is>
       </c>
       <c r="D53" t="n">
-        <v>1709700346</v>
+        <v>1712230638</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
@@ -2341,6 +2397,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -2359,7 +2416,7 @@
         </is>
       </c>
       <c r="D54" t="n">
-        <v>1709701032</v>
+        <v>1712275905</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
@@ -2377,6 +2434,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -2395,7 +2453,7 @@
         </is>
       </c>
       <c r="D55" t="n">
-        <v>1709707820</v>
+        <v>1712299643</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
@@ -2413,6 +2471,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -2431,7 +2490,7 @@
         </is>
       </c>
       <c r="D56" t="n">
-        <v>1709722068</v>
+        <v>1712301033</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
@@ -2449,6 +2508,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
@@ -2467,7 +2527,7 @@
         </is>
       </c>
       <c r="D57" t="n">
-        <v>1709772006</v>
+        <v>1712308943</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
@@ -2477,7 +2537,7 @@
       <c r="F57" t="inlineStr"/>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
@@ -2485,6 +2545,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -2503,7 +2564,7 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>1709772140</v>
+        <v>1712378350</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
@@ -2521,6 +2582,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -2539,7 +2601,7 @@
         </is>
       </c>
       <c r="D59" t="n">
-        <v>1709774127</v>
+        <v>1712378443</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
@@ -2557,6 +2619,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -2575,7 +2638,7 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>1709775676</v>
+        <v>1712389105</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
@@ -2593,6 +2656,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -2611,7 +2675,7 @@
         </is>
       </c>
       <c r="D61" t="n">
-        <v>1709776127</v>
+        <v>1712389729</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
@@ -2629,6 +2693,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -2647,7 +2712,7 @@
         </is>
       </c>
       <c r="D62" t="n">
-        <v>1709783851</v>
+        <v>1712391813</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
@@ -2657,7 +2722,7 @@
       <c r="F62" t="inlineStr"/>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
@@ -2665,6 +2730,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
@@ -2683,7 +2749,7 @@
         </is>
       </c>
       <c r="D63" t="n">
-        <v>1709784016</v>
+        <v>1712419783</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
@@ -2701,6 +2767,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -2719,7 +2786,7 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>1709784985</v>
+        <v>1712464606</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
@@ -2737,6 +2804,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -2755,7 +2823,7 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>1709786367</v>
+        <v>1712464783</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
@@ -2773,6 +2841,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
@@ -2791,7 +2860,7 @@
         </is>
       </c>
       <c r="D66" t="n">
-        <v>1709791306</v>
+        <v>1712470838</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
@@ -2809,6 +2878,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
@@ -2827,7 +2897,7 @@
         </is>
       </c>
       <c r="D67" t="n">
-        <v>1709792619</v>
+        <v>1712475250</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
@@ -2845,6 +2915,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
@@ -2863,7 +2934,7 @@
         </is>
       </c>
       <c r="D68" t="n">
-        <v>1709793153</v>
+        <v>1712493604</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
@@ -2881,6 +2952,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -2899,7 +2971,7 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>1709804133</v>
+        <v>1712497322</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
@@ -2917,6 +2989,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -2935,7 +3008,7 @@
         </is>
       </c>
       <c r="D70" t="n">
-        <v>1709849029</v>
+        <v>1712536792</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
@@ -2945,7 +3018,7 @@
       <c r="F70" t="inlineStr"/>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
@@ -2953,6 +3026,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -2971,7 +3045,7 @@
         </is>
       </c>
       <c r="D71" t="n">
-        <v>1709849220</v>
+        <v>1712551850</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
@@ -2989,6 +3063,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
@@ -3007,7 +3082,7 @@
         </is>
       </c>
       <c r="D72" t="n">
-        <v>1709851173</v>
+        <v>1712555429</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
@@ -3025,6 +3100,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
@@ -3043,7 +3119,7 @@
         </is>
       </c>
       <c r="D73" t="n">
-        <v>1709868137</v>
+        <v>1712558167</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
@@ -3061,6 +3137,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
@@ -3079,7 +3156,7 @@
         </is>
       </c>
       <c r="D74" t="n">
-        <v>1709868968</v>
+        <v>1712562620</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
@@ -3097,6 +3174,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
@@ -3115,7 +3193,7 @@
         </is>
       </c>
       <c r="D75" t="n">
-        <v>1709871754</v>
+        <v>1712622884</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
@@ -3133,6 +3211,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
@@ -3151,7 +3230,7 @@
         </is>
       </c>
       <c r="D76" t="n">
-        <v>1709936155</v>
+        <v>1712636762</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
@@ -3169,6 +3248,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
@@ -3187,7 +3267,7 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>1709936398</v>
+        <v>1712637038</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
@@ -3205,6 +3285,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
@@ -3223,7 +3304,7 @@
         </is>
       </c>
       <c r="D78" t="n">
-        <v>1709938094</v>
+        <v>1712639243</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
@@ -3241,6 +3322,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
@@ -3259,7 +3341,7 @@
         </is>
       </c>
       <c r="D79" t="n">
-        <v>1709950351</v>
+        <v>1712642711</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
@@ -3269,7 +3351,7 @@
       <c r="F79" t="inlineStr"/>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3277,6 +3359,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
@@ -3295,7 +3378,7 @@
         </is>
       </c>
       <c r="D80" t="n">
-        <v>1709950419</v>
+        <v>1712647954</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
@@ -3313,6 +3396,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
@@ -3331,7 +3415,7 @@
         </is>
       </c>
       <c r="D81" t="n">
-        <v>1709953656</v>
+        <v>1712708685</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
@@ -3349,6 +3433,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
@@ -3367,7 +3452,7 @@
         </is>
       </c>
       <c r="D82" t="n">
-        <v>1709959219</v>
+        <v>1712730087</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
@@ -3377,7 +3462,7 @@
       <c r="F82" t="inlineStr"/>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
@@ -3385,6 +3470,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
@@ -3403,7 +3489,7 @@
         </is>
       </c>
       <c r="D83" t="n">
-        <v>1709959352</v>
+        <v>1712730518</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
@@ -3421,6 +3507,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
@@ -3439,7 +3526,7 @@
         </is>
       </c>
       <c r="D84" t="n">
-        <v>1709961446</v>
+        <v>1712742753</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
@@ -3457,6 +3544,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
@@ -3475,7 +3563,7 @@
         </is>
       </c>
       <c r="D85" t="n">
-        <v>1709962144</v>
+        <v>1712795263</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
@@ -3493,6 +3581,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
@@ -3511,7 +3600,7 @@
         </is>
       </c>
       <c r="D86" t="n">
-        <v>1710025769</v>
+        <v>1712814019</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
@@ -3529,6 +3618,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
@@ -3547,7 +3637,7 @@
         </is>
       </c>
       <c r="D87" t="n">
-        <v>1710041253</v>
+        <v>1712816188</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
@@ -3565,6 +3655,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
@@ -3583,7 +3674,7 @@
         </is>
       </c>
       <c r="D88" t="n">
-        <v>1710043410</v>
+        <v>1712816876</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
@@ -3601,6 +3692,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
@@ -3619,7 +3711,7 @@
         </is>
       </c>
       <c r="D89" t="n">
-        <v>1710050158</v>
+        <v>1712881945</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
@@ -3637,6 +3729,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
@@ -3655,7 +3748,7 @@
         </is>
       </c>
       <c r="D90" t="n">
-        <v>1710111352</v>
+        <v>1712903458</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
@@ -3673,6 +3766,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
@@ -3691,7 +3785,7 @@
         </is>
       </c>
       <c r="D91" t="n">
-        <v>1710121646</v>
+        <v>1712906541</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
@@ -3701,7 +3795,7 @@
       <c r="F91" t="inlineStr"/>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -3709,6 +3803,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
@@ -3727,7 +3822,7 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>1710121781</v>
+        <v>1712908842</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
@@ -3745,6 +3840,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
@@ -3763,7 +3859,7 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>1710123528</v>
+        <v>1712922034</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
@@ -3781,6 +3877,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
@@ -3799,7 +3896,7 @@
         </is>
       </c>
       <c r="D94" t="n">
-        <v>1710129247</v>
+        <v>1712981184</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
@@ -3817,6 +3914,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
@@ -3835,7 +3933,7 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>1710134916</v>
+        <v>1712988786</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
@@ -3853,6 +3951,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
@@ -3871,7 +3970,7 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>1710141183</v>
+        <v>1712992114</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
@@ -3889,6 +3988,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
@@ -3907,7 +4007,7 @@
         </is>
       </c>
       <c r="D97" t="n">
-        <v>1710141263</v>
+        <v>1712992328</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
@@ -3925,6 +4025,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
@@ -3943,7 +4044,7 @@
         </is>
       </c>
       <c r="D98" t="n">
-        <v>1710144556</v>
+        <v>1712994510</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
@@ -3961,6 +4062,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
@@ -3979,7 +4081,7 @@
         </is>
       </c>
       <c r="D99" t="n">
-        <v>1710145015</v>
+        <v>1712994673</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
@@ -3997,6 +4099,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
@@ -4015,7 +4118,7 @@
         </is>
       </c>
       <c r="D100" t="n">
-        <v>1710199586</v>
+        <v>1713007480</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
@@ -4033,6 +4136,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
@@ -4051,7 +4155,7 @@
         </is>
       </c>
       <c r="D101" t="n">
-        <v>1710212354</v>
+        <v>1713023246</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
@@ -4061,7 +4165,7 @@
       <c r="F101" t="inlineStr"/>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4069,6 +4173,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
@@ -4087,7 +4192,7 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>1710212495</v>
+        <v>1713059496</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
@@ -4105,6 +4210,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
@@ -4123,7 +4229,7 @@
         </is>
       </c>
       <c r="D103" t="n">
-        <v>1710212943</v>
+        <v>1713063982</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
@@ -4141,6 +4247,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
@@ -4159,7 +4266,7 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>1710214611</v>
+        <v>1713068882</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
@@ -4177,6 +4284,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
@@ -4195,7 +4303,7 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>1710225539</v>
+        <v>1713072378</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
@@ -4213,6 +4321,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
@@ -4231,7 +4340,7 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>1710231109</v>
+        <v>1713081877</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
@@ -4249,6 +4358,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
@@ -4267,7 +4377,7 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>1710232685</v>
+        <v>1713086757</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
@@ -4277,7 +4387,7 @@
       <c r="F107" t="inlineStr"/>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
@@ -4285,6 +4395,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
@@ -4303,7 +4414,7 @@
         </is>
       </c>
       <c r="D108" t="n">
-        <v>1710232908</v>
+        <v>1713086976</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
@@ -4321,6 +4432,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
@@ -4339,7 +4451,7 @@
         </is>
       </c>
       <c r="D109" t="n">
-        <v>1710236227</v>
+        <v>1713096641</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
@@ -4357,6 +4469,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
@@ -4375,7 +4488,7 @@
         </is>
       </c>
       <c r="D110" t="n">
-        <v>1710292815</v>
+        <v>1713114765</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
@@ -4393,6 +4506,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
@@ -4411,7 +4525,7 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>1710297875</v>
+        <v>1713140113</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
@@ -4429,6 +4543,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
@@ -4447,7 +4562,7 @@
         </is>
       </c>
       <c r="D112" t="n">
-        <v>1710303144</v>
+        <v>1713160378</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
@@ -4457,7 +4572,7 @@
       <c r="F112" t="inlineStr"/>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
@@ -4465,6 +4580,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
@@ -4483,7 +4599,7 @@
         </is>
       </c>
       <c r="D113" t="n">
-        <v>1710308547</v>
+        <v>1713160551</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
@@ -4501,6 +4617,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
@@ -4519,7 +4636,7 @@
         </is>
       </c>
       <c r="D114" t="n">
-        <v>1710311796</v>
+        <v>1713162650</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
@@ -4537,6 +4654,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
@@ -4555,7 +4673,7 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>1710315977</v>
+        <v>1713171026</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
@@ -4573,6 +4691,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
@@ -4591,7 +4710,7 @@
         </is>
       </c>
       <c r="D116" t="n">
-        <v>1710334506</v>
+        <v>1713171093</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
@@ -4609,6 +4728,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
@@ -4627,7 +4747,7 @@
         </is>
       </c>
       <c r="D117" t="n">
-        <v>1710382729</v>
+        <v>1713183769</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
@@ -4637,7 +4757,7 @@
       <c r="F117" t="inlineStr"/>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
@@ -4645,6 +4765,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
@@ -4663,7 +4784,7 @@
         </is>
       </c>
       <c r="D118" t="n">
-        <v>1710383983</v>
+        <v>1713184044</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
@@ -4681,6 +4802,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
@@ -4699,7 +4821,7 @@
         </is>
       </c>
       <c r="D119" t="n">
-        <v>1710392859</v>
+        <v>1713186367</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
@@ -4717,6 +4839,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
@@ -4735,7 +4858,7 @@
         </is>
       </c>
       <c r="D120" t="n">
-        <v>1710394944</v>
+        <v>1713224386</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
@@ -4745,7 +4868,7 @@
       <c r="F120" t="inlineStr"/>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
@@ -4753,6 +4876,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
@@ -4771,7 +4895,7 @@
         </is>
       </c>
       <c r="D121" t="n">
-        <v>1710397738</v>
+        <v>1713224627</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
@@ -4789,6 +4913,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
@@ -4807,7 +4932,7 @@
         </is>
       </c>
       <c r="D122" t="n">
-        <v>1710412575</v>
+        <v>1713228633</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
@@ -4825,6 +4950,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
@@ -4843,7 +4969,7 @@
         </is>
       </c>
       <c r="D123" t="n">
-        <v>1710458565</v>
+        <v>1713246815</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
@@ -4861,6 +4987,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
@@ -4879,7 +5006,7 @@
         </is>
       </c>
       <c r="D124" t="n">
-        <v>1710475907</v>
+        <v>1713248536</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
@@ -4897,6 +5024,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
@@ -4915,7 +5043,7 @@
         </is>
       </c>
       <c r="D125" t="n">
-        <v>1710479514</v>
+        <v>1713249575</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
@@ -4925,7 +5053,7 @@
       <c r="F125" t="inlineStr"/>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
@@ -4933,6 +5061,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
@@ -4951,7 +5080,7 @@
         </is>
       </c>
       <c r="D126" t="n">
-        <v>1710484442</v>
+        <v>1713249723</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
@@ -4969,6 +5098,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
@@ -4987,7 +5117,7 @@
         </is>
       </c>
       <c r="D127" t="n">
-        <v>1710542705</v>
+        <v>1713253842</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
@@ -5005,6 +5135,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
@@ -5023,7 +5154,7 @@
         </is>
       </c>
       <c r="D128" t="n">
-        <v>1710559457</v>
+        <v>1713260679</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
@@ -5041,6 +5172,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
@@ -5059,7 +5191,7 @@
         </is>
       </c>
       <c r="D129" t="n">
-        <v>1710561011</v>
+        <v>1713314706</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
@@ -5069,7 +5201,7 @@
       <c r="F129" t="inlineStr"/>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
@@ -5077,6 +5209,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I129" t="inlineStr"/>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
@@ -5095,7 +5228,7 @@
         </is>
       </c>
       <c r="D130" t="n">
-        <v>1710561127</v>
+        <v>1713333406</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
@@ -5105,7 +5238,7 @@
       <c r="F130" t="inlineStr"/>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
@@ -5113,6 +5246,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
@@ -5131,7 +5265,7 @@
         </is>
       </c>
       <c r="D131" t="n">
-        <v>1710563451</v>
+        <v>1713333515</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
@@ -5149,6 +5283,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
@@ -5167,7 +5302,7 @@
         </is>
       </c>
       <c r="D132" t="n">
-        <v>1710563606</v>
+        <v>1713335639</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
@@ -5185,6 +5320,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
@@ -5203,7 +5339,7 @@
         </is>
       </c>
       <c r="D133" t="n">
-        <v>1710629774</v>
+        <v>1713335798</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
@@ -5221,6 +5357,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I133" t="inlineStr"/>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
@@ -5239,7 +5376,7 @@
         </is>
       </c>
       <c r="D134" t="n">
-        <v>1710644660</v>
+        <v>1713337075</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
@@ -5257,6 +5394,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
@@ -5275,7 +5413,7 @@
         </is>
       </c>
       <c r="D135" t="n">
-        <v>1710645805</v>
+        <v>1713338369</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
@@ -5285,7 +5423,7 @@
       <c r="F135" t="inlineStr"/>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
@@ -5293,6 +5431,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
@@ -5311,7 +5450,7 @@
         </is>
       </c>
       <c r="D136" t="n">
-        <v>1710654327</v>
+        <v>1713338520</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
@@ -5329,6 +5468,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
@@ -5347,7 +5487,7 @@
         </is>
       </c>
       <c r="D137" t="n">
-        <v>1710655645</v>
+        <v>1713342421</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
@@ -5365,6 +5505,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
@@ -5383,7 +5524,7 @@
         </is>
       </c>
       <c r="D138" t="n">
-        <v>1710667001</v>
+        <v>1713345027</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
@@ -5401,6 +5542,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
@@ -5419,7 +5561,7 @@
         </is>
       </c>
       <c r="D139" t="n">
-        <v>1710713463</v>
+        <v>1713399315</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
@@ -5429,7 +5571,7 @@
       <c r="F139" t="inlineStr"/>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
@@ -5437,6 +5579,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
@@ -5455,7 +5598,7 @@
         </is>
       </c>
       <c r="D140" t="n">
-        <v>1710713665</v>
+        <v>1713424825</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
@@ -5473,6 +5616,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
@@ -5491,7 +5635,7 @@
         </is>
       </c>
       <c r="D141" t="n">
-        <v>1710716346</v>
+        <v>1713433080</v>
       </c>
       <c r="E141" t="inlineStr">
         <is>
@@ -5509,6 +5653,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
@@ -5527,7 +5672,7 @@
         </is>
       </c>
       <c r="D142" t="n">
-        <v>1710727929</v>
+        <v>1713433816</v>
       </c>
       <c r="E142" t="inlineStr">
         <is>
@@ -5545,6 +5690,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I142" t="inlineStr"/>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
@@ -5563,7 +5709,7 @@
         </is>
       </c>
       <c r="D143" t="n">
-        <v>1710733770</v>
+        <v>1713487130</v>
       </c>
       <c r="E143" t="inlineStr">
         <is>
@@ -5581,6 +5727,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
@@ -5599,7 +5746,7 @@
         </is>
       </c>
       <c r="D144" t="n">
-        <v>1710741578</v>
+        <v>1713506942</v>
       </c>
       <c r="E144" t="inlineStr">
         <is>
@@ -5617,6 +5764,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I144" t="inlineStr"/>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
@@ -5635,7 +5783,7 @@
         </is>
       </c>
       <c r="D145" t="n">
-        <v>1710801515</v>
+        <v>1713515609</v>
       </c>
       <c r="E145" t="inlineStr">
         <is>
@@ -5653,6 +5801,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I145" t="inlineStr"/>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
@@ -5671,7 +5820,7 @@
         </is>
       </c>
       <c r="D146" t="n">
-        <v>1710814775</v>
+        <v>1713520100</v>
       </c>
       <c r="E146" t="inlineStr">
         <is>
@@ -5681,7 +5830,7 @@
       <c r="F146" t="inlineStr"/>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
@@ -5689,6 +5838,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I146" t="inlineStr"/>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
@@ -5707,7 +5857,7 @@
         </is>
       </c>
       <c r="D147" t="n">
-        <v>1710814907</v>
+        <v>1713583785</v>
       </c>
       <c r="E147" t="inlineStr">
         <is>
@@ -5717,7 +5867,7 @@
       <c r="F147" t="inlineStr"/>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
@@ -5725,6 +5875,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I147" t="inlineStr"/>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
@@ -5743,7 +5894,7 @@
         </is>
       </c>
       <c r="D148" t="n">
-        <v>1710818263</v>
+        <v>1713583986</v>
       </c>
       <c r="E148" t="inlineStr">
         <is>
@@ -5761,6 +5912,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
@@ -5779,7 +5931,7 @@
         </is>
       </c>
       <c r="D149" t="n">
-        <v>1710823415</v>
+        <v>1713587766</v>
       </c>
       <c r="E149" t="inlineStr">
         <is>
@@ -5797,6 +5949,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I149" t="inlineStr"/>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
@@ -5815,7 +5968,7 @@
         </is>
       </c>
       <c r="D150" t="n">
-        <v>1710825691</v>
+        <v>1713588764</v>
       </c>
       <c r="E150" t="inlineStr">
         <is>
@@ -5825,7 +5978,7 @@
       <c r="F150" t="inlineStr"/>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
@@ -5833,6 +5986,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I150" t="inlineStr"/>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
@@ -5851,7 +6005,7 @@
         </is>
       </c>
       <c r="D151" t="n">
-        <v>1710825891</v>
+        <v>1713602234</v>
       </c>
       <c r="E151" t="inlineStr">
         <is>
@@ -5869,6 +6023,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I151" t="inlineStr"/>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
@@ -5887,7 +6042,7 @@
         </is>
       </c>
       <c r="D152" t="n">
-        <v>1710828885</v>
+        <v>1713604207</v>
       </c>
       <c r="E152" t="inlineStr">
         <is>
@@ -5905,6 +6060,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I152" t="inlineStr"/>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
@@ -5923,7 +6079,7 @@
         </is>
       </c>
       <c r="D153" t="n">
-        <v>1710898480</v>
+        <v>1713608270</v>
       </c>
       <c r="E153" t="inlineStr">
         <is>
@@ -5941,6 +6097,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I153" t="inlineStr"/>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
@@ -5959,7 +6116,7 @@
         </is>
       </c>
       <c r="D154" t="n">
-        <v>1710901778</v>
+        <v>1713631806</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
@@ -5977,6 +6134,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
@@ -5995,7 +6153,7 @@
         </is>
       </c>
       <c r="D155" t="n">
-        <v>1710907050</v>
+        <v>1713672494</v>
       </c>
       <c r="E155" t="inlineStr">
         <is>
@@ -6013,6 +6171,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I155" t="inlineStr"/>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
@@ -6031,7 +6190,7 @@
         </is>
       </c>
       <c r="D156" t="n">
-        <v>1710908161</v>
+        <v>1713673407</v>
       </c>
       <c r="E156" t="inlineStr">
         <is>
@@ -6049,6 +6208,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I156" t="inlineStr"/>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
@@ -6067,7 +6227,7 @@
         </is>
       </c>
       <c r="D157" t="n">
-        <v>1710910547</v>
+        <v>1713680194</v>
       </c>
       <c r="E157" t="inlineStr">
         <is>
@@ -6085,6 +6245,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
@@ -6103,7 +6264,7 @@
         </is>
       </c>
       <c r="D158" t="n">
-        <v>1710916317</v>
+        <v>1713684148</v>
       </c>
       <c r="E158" t="inlineStr">
         <is>
@@ -6121,6 +6282,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I158" t="inlineStr"/>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
@@ -6139,7 +6301,7 @@
         </is>
       </c>
       <c r="D159" t="n">
-        <v>1710933644</v>
+        <v>1713697181</v>
       </c>
       <c r="E159" t="inlineStr">
         <is>
@@ -6157,6 +6319,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I159" t="inlineStr"/>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
@@ -6175,7 +6338,7 @@
         </is>
       </c>
       <c r="D160" t="n">
-        <v>1710985847</v>
+        <v>1713713139</v>
       </c>
       <c r="E160" t="inlineStr">
         <is>
@@ -6193,6 +6356,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I160" t="inlineStr"/>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
@@ -6211,7 +6375,7 @@
         </is>
       </c>
       <c r="D161" t="n">
-        <v>1710989811</v>
+        <v>1713741436</v>
       </c>
       <c r="E161" t="inlineStr">
         <is>
@@ -6221,7 +6385,7 @@
       <c r="F161" t="inlineStr"/>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
@@ -6229,6 +6393,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I161" t="inlineStr"/>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
@@ -6247,7 +6412,7 @@
         </is>
       </c>
       <c r="D162" t="n">
-        <v>1710996738</v>
+        <v>1713741637</v>
       </c>
       <c r="E162" t="inlineStr">
         <is>
@@ -6265,6 +6430,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I162" t="inlineStr"/>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
@@ -6283,7 +6449,7 @@
         </is>
       </c>
       <c r="D163" t="n">
-        <v>1710998532</v>
+        <v>1713744629</v>
       </c>
       <c r="E163" t="inlineStr">
         <is>
@@ -6301,6 +6467,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I163" t="inlineStr"/>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
@@ -6319,7 +6486,7 @@
         </is>
       </c>
       <c r="D164" t="n">
-        <v>1711002678</v>
+        <v>1713765568</v>
       </c>
       <c r="E164" t="inlineStr">
         <is>
@@ -6329,7 +6496,7 @@
       <c r="F164" t="inlineStr"/>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
@@ -6337,6 +6504,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I164" t="inlineStr"/>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
@@ -6355,7 +6523,7 @@
         </is>
       </c>
       <c r="D165" t="n">
-        <v>1711002888</v>
+        <v>1713765697</v>
       </c>
       <c r="E165" t="inlineStr">
         <is>
@@ -6373,6 +6541,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I165" t="inlineStr"/>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
@@ -6391,7 +6560,7 @@
         </is>
       </c>
       <c r="D166" t="n">
-        <v>1711004564</v>
+        <v>1713772299</v>
       </c>
       <c r="E166" t="inlineStr">
         <is>
@@ -6401,7 +6570,7 @@
       <c r="F166" t="inlineStr"/>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
@@ -6409,6 +6578,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I166" t="inlineStr"/>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
@@ -6427,7 +6597,7 @@
         </is>
       </c>
       <c r="D167" t="n">
-        <v>1711016429</v>
+        <v>1713772512</v>
       </c>
       <c r="E167" t="inlineStr">
         <is>
@@ -6437,7 +6607,7 @@
       <c r="F167" t="inlineStr"/>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
@@ -6445,6 +6615,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I167" t="inlineStr"/>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
@@ -6463,7 +6634,7 @@
         </is>
       </c>
       <c r="D168" t="n">
-        <v>1711016575</v>
+        <v>1713776052</v>
       </c>
       <c r="E168" t="inlineStr">
         <is>
@@ -6481,6 +6652,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I168" t="inlineStr"/>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
@@ -6499,7 +6671,7 @@
         </is>
       </c>
       <c r="D169" t="n">
-        <v>1711019363</v>
+        <v>1713832515</v>
       </c>
       <c r="E169" t="inlineStr">
         <is>
@@ -6517,6 +6689,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I169" t="inlineStr"/>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
@@ -6535,7 +6708,7 @@
         </is>
       </c>
       <c r="D170" t="n">
-        <v>1711061394</v>
+        <v>1713852612</v>
       </c>
       <c r="E170" t="inlineStr">
         <is>
@@ -6553,6 +6726,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I170" t="inlineStr"/>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
@@ -6571,7 +6745,7 @@
         </is>
       </c>
       <c r="D171" t="n">
-        <v>1711075617</v>
+        <v>1713856200</v>
       </c>
       <c r="E171" t="inlineStr">
         <is>
@@ -6589,6 +6763,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I171" t="inlineStr"/>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
@@ -6607,7 +6782,7 @@
         </is>
       </c>
       <c r="D172" t="n">
-        <v>1711075707</v>
+        <v>1713856293</v>
       </c>
       <c r="E172" t="inlineStr">
         <is>
@@ -6625,6 +6800,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I172" t="inlineStr"/>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
@@ -6643,7 +6819,7 @@
         </is>
       </c>
       <c r="D173" t="n">
-        <v>1711077805</v>
+        <v>1713856404</v>
       </c>
       <c r="E173" t="inlineStr">
         <is>
@@ -6653,7 +6829,7 @@
       <c r="F173" t="inlineStr"/>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
@@ -6661,6 +6837,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I173" t="inlineStr"/>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
@@ -6679,7 +6856,7 @@
         </is>
       </c>
       <c r="D174" t="n">
-        <v>1711078737</v>
+        <v>1713856627</v>
       </c>
       <c r="E174" t="inlineStr">
         <is>
@@ -6689,7 +6866,7 @@
       <c r="F174" t="inlineStr"/>
       <c r="G174" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H174" t="inlineStr">
@@ -6697,6 +6874,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I174" t="inlineStr"/>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
@@ -6715,7 +6893,7 @@
         </is>
       </c>
       <c r="D175" t="n">
-        <v>1711078807</v>
+        <v>1713859094</v>
       </c>
       <c r="E175" t="inlineStr">
         <is>
@@ -6733,6 +6911,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I175" t="inlineStr"/>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
@@ -6751,7 +6930,7 @@
         </is>
       </c>
       <c r="D176" t="n">
-        <v>1711081779</v>
+        <v>1713859913</v>
       </c>
       <c r="E176" t="inlineStr">
         <is>
@@ -6769,6 +6948,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I176" t="inlineStr"/>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
@@ -6787,7 +6967,7 @@
         </is>
       </c>
       <c r="D177" t="n">
-        <v>1711085254</v>
+        <v>1713861194</v>
       </c>
       <c r="E177" t="inlineStr">
         <is>
@@ -6805,6 +6985,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I177" t="inlineStr"/>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
@@ -6823,7 +7004,7 @@
         </is>
       </c>
       <c r="D178" t="n">
-        <v>1711087190</v>
+        <v>1713915668</v>
       </c>
       <c r="E178" t="inlineStr">
         <is>
@@ -6841,6 +7022,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I178" t="inlineStr"/>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
@@ -6859,7 +7041,7 @@
         </is>
       </c>
       <c r="D179" t="n">
-        <v>1711087290</v>
+        <v>1713915818</v>
       </c>
       <c r="E179" t="inlineStr">
         <is>
@@ -6877,6 +7059,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I179" t="inlineStr"/>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
@@ -6895,7 +7078,7 @@
         </is>
       </c>
       <c r="D180" t="n">
-        <v>1711089501</v>
+        <v>1713918514</v>
       </c>
       <c r="E180" t="inlineStr">
         <is>
@@ -6913,6 +7096,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I180" t="inlineStr"/>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
@@ -6931,7 +7115,7 @@
         </is>
       </c>
       <c r="D181" t="n">
-        <v>1711093031</v>
+        <v>1713937831</v>
       </c>
       <c r="E181" t="inlineStr">
         <is>
@@ -6949,6 +7133,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I181" t="inlineStr"/>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
@@ -6967,7 +7152,7 @@
         </is>
       </c>
       <c r="D182" t="n">
-        <v>1711147856</v>
+        <v>1713945792</v>
       </c>
       <c r="E182" t="inlineStr">
         <is>
@@ -6985,6 +7170,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I182" t="inlineStr"/>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
@@ -7003,7 +7189,7 @@
         </is>
       </c>
       <c r="D183" t="n">
-        <v>1711160671</v>
+        <v>1713947182</v>
       </c>
       <c r="E183" t="inlineStr">
         <is>
@@ -7013,7 +7199,7 @@
       <c r="F183" t="inlineStr"/>
       <c r="G183" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H183" t="inlineStr">
@@ -7021,6 +7207,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I183" t="inlineStr"/>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
@@ -7039,7 +7226,7 @@
         </is>
       </c>
       <c r="D184" t="n">
-        <v>1711160775</v>
+        <v>1713963386</v>
       </c>
       <c r="E184" t="inlineStr">
         <is>
@@ -7057,6 +7244,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I184" t="inlineStr"/>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
@@ -7075,7 +7263,7 @@
         </is>
       </c>
       <c r="D185" t="n">
-        <v>1711163427</v>
+        <v>1714005303</v>
       </c>
       <c r="E185" t="inlineStr">
         <is>
@@ -7093,6 +7281,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I185" t="inlineStr"/>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
@@ -7111,7 +7300,7 @@
         </is>
       </c>
       <c r="D186" t="n">
-        <v>1711164453</v>
+        <v>1714025874</v>
       </c>
       <c r="E186" t="inlineStr">
         <is>
@@ -7129,6 +7318,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I186" t="inlineStr"/>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
@@ -7147,7 +7337,7 @@
         </is>
       </c>
       <c r="D187" t="n">
-        <v>1711171908</v>
+        <v>1714029109</v>
       </c>
       <c r="E187" t="inlineStr">
         <is>
@@ -7165,6 +7355,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I187" t="inlineStr"/>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
@@ -7183,7 +7374,7 @@
         </is>
       </c>
       <c r="D188" t="n">
-        <v>1711233534</v>
+        <v>1714037613</v>
       </c>
       <c r="E188" t="inlineStr">
         <is>
@@ -7193,7 +7384,7 @@
       <c r="F188" t="inlineStr"/>
       <c r="G188" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H188" t="inlineStr">
@@ -7201,6 +7392,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I188" t="inlineStr"/>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
@@ -7219,7 +7411,7 @@
         </is>
       </c>
       <c r="D189" t="n">
-        <v>1711233781</v>
+        <v>1714091251</v>
       </c>
       <c r="E189" t="inlineStr">
         <is>
@@ -7237,6 +7429,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I189" t="inlineStr"/>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
@@ -7255,7 +7448,7 @@
         </is>
       </c>
       <c r="D190" t="n">
-        <v>1711236484</v>
+        <v>1714112846</v>
       </c>
       <c r="E190" t="inlineStr">
         <is>
@@ -7273,6 +7466,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I190" t="inlineStr"/>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
@@ -7291,7 +7485,7 @@
         </is>
       </c>
       <c r="D191" t="n">
-        <v>1711256469</v>
+        <v>1714122996</v>
       </c>
       <c r="E191" t="inlineStr">
         <is>
@@ -7309,6 +7503,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I191" t="inlineStr"/>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
@@ -7327,7 +7522,7 @@
         </is>
       </c>
       <c r="D192" t="n">
-        <v>1711261176</v>
+        <v>1714123400</v>
       </c>
       <c r="E192" t="inlineStr">
         <is>
@@ -7345,6 +7540,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I192" t="inlineStr"/>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
@@ -7363,7 +7559,7 @@
         </is>
       </c>
       <c r="D193" t="n">
-        <v>1711263049</v>
+        <v>1714183649</v>
       </c>
       <c r="E193" t="inlineStr">
         <is>
@@ -7381,6 +7577,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I193" t="inlineStr"/>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
@@ -7399,7 +7596,7 @@
         </is>
       </c>
       <c r="D194" t="n">
-        <v>1711319980</v>
+        <v>1714190810</v>
       </c>
       <c r="E194" t="inlineStr">
         <is>
@@ -7409,7 +7606,7 @@
       <c r="F194" t="inlineStr"/>
       <c r="G194" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H194" t="inlineStr">
@@ -7417,6 +7614,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I194" t="inlineStr"/>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
@@ -7435,7 +7633,7 @@
         </is>
       </c>
       <c r="D195" t="n">
-        <v>1711320243</v>
+        <v>1714194185</v>
       </c>
       <c r="E195" t="inlineStr">
         <is>
@@ -7453,6 +7651,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I195" t="inlineStr"/>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
@@ -7471,7 +7670,7 @@
         </is>
       </c>
       <c r="D196" t="n">
-        <v>1711323850</v>
+        <v>1714205709</v>
       </c>
       <c r="E196" t="inlineStr">
         <is>
@@ -7489,6 +7688,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I196" t="inlineStr"/>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
@@ -7507,7 +7707,7 @@
         </is>
       </c>
       <c r="D197" t="n">
-        <v>1711338164</v>
+        <v>1714206331</v>
       </c>
       <c r="E197" t="inlineStr">
         <is>
@@ -7525,6 +7725,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I197" t="inlineStr"/>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
@@ -7543,7 +7744,7 @@
         </is>
       </c>
       <c r="D198" t="n">
-        <v>1711339079</v>
+        <v>1714217291</v>
       </c>
       <c r="E198" t="inlineStr">
         <is>
@@ -7553,7 +7754,7 @@
       <c r="F198" t="inlineStr"/>
       <c r="G198" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H198" t="inlineStr">
@@ -7561,6 +7762,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I198" t="inlineStr"/>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
@@ -7579,7 +7781,7 @@
         </is>
       </c>
       <c r="D199" t="n">
-        <v>1711339233</v>
+        <v>1714238154</v>
       </c>
       <c r="E199" t="inlineStr">
         <is>
@@ -7597,6 +7799,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I199" t="inlineStr"/>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
@@ -7615,7 +7818,7 @@
         </is>
       </c>
       <c r="D200" t="n">
-        <v>1711342142</v>
+        <v>1714275891</v>
       </c>
       <c r="E200" t="inlineStr">
         <is>
@@ -7625,7 +7828,7 @@
       <c r="F200" t="inlineStr"/>
       <c r="G200" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H200" t="inlineStr">
@@ -7633,6 +7836,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I200" t="inlineStr"/>
     </row>
     <row r="201">
       <c r="A201" t="inlineStr">
@@ -7651,7 +7855,7 @@
         </is>
       </c>
       <c r="D201" t="n">
-        <v>1711342686</v>
+        <v>1714276137</v>
       </c>
       <c r="E201" t="inlineStr">
         <is>
@@ -7661,7 +7865,7 @@
       <c r="F201" t="inlineStr"/>
       <c r="G201" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H201" t="inlineStr">
@@ -7669,6 +7873,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I201" t="inlineStr"/>
     </row>
     <row r="202">
       <c r="A202" t="inlineStr">
@@ -7687,7 +7892,7 @@
         </is>
       </c>
       <c r="D202" t="n">
-        <v>1711342801</v>
+        <v>1714276500</v>
       </c>
       <c r="E202" t="inlineStr">
         <is>
@@ -7697,7 +7902,7 @@
       <c r="F202" t="inlineStr"/>
       <c r="G202" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H202" t="inlineStr">
@@ -7705,6 +7910,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I202" t="inlineStr"/>
     </row>
     <row r="203">
       <c r="A203" t="inlineStr">
@@ -7723,7 +7929,7 @@
         </is>
       </c>
       <c r="D203" t="n">
-        <v>1711345356</v>
+        <v>1714276594</v>
       </c>
       <c r="E203" t="inlineStr">
         <is>
@@ -7741,6 +7947,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I203" t="inlineStr"/>
     </row>
     <row r="204">
       <c r="A204" t="inlineStr">
@@ -7759,7 +7966,7 @@
         </is>
       </c>
       <c r="D204" t="n">
-        <v>1711349599</v>
+        <v>1714278246</v>
       </c>
       <c r="E204" t="inlineStr">
         <is>
@@ -7769,7 +7976,7 @@
       <c r="F204" t="inlineStr"/>
       <c r="G204" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H204" t="inlineStr">
@@ -7777,6 +7984,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I204" t="inlineStr"/>
     </row>
     <row r="205">
       <c r="A205" t="inlineStr">
@@ -7795,7 +8003,7 @@
         </is>
       </c>
       <c r="D205" t="n">
-        <v>1711349769</v>
+        <v>1714280042</v>
       </c>
       <c r="E205" t="inlineStr">
         <is>
@@ -7813,6 +8021,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I205" t="inlineStr"/>
     </row>
     <row r="206">
       <c r="A206" t="inlineStr">
@@ -7831,7 +8040,7 @@
         </is>
       </c>
       <c r="D206" t="n">
-        <v>1711352349</v>
+        <v>1714288222</v>
       </c>
       <c r="E206" t="inlineStr">
         <is>
@@ -7849,6 +8058,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I206" t="inlineStr"/>
     </row>
     <row r="207">
       <c r="A207" t="inlineStr">
@@ -7867,7 +8077,7 @@
         </is>
       </c>
       <c r="D207" t="n">
-        <v>1711413981</v>
+        <v>1714291830</v>
       </c>
       <c r="E207" t="inlineStr">
         <is>
@@ -7885,6 +8095,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I207" t="inlineStr"/>
     </row>
     <row r="208">
       <c r="A208" t="inlineStr">
@@ -7903,7 +8114,7 @@
         </is>
       </c>
       <c r="D208" t="n">
-        <v>1711435573</v>
+        <v>1714302923</v>
       </c>
       <c r="E208" t="inlineStr">
         <is>
@@ -7913,7 +8124,7 @@
       <c r="F208" t="inlineStr"/>
       <c r="G208" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
+          <t>Kitchen.MicrowaveOven001.state: off</t>
         </is>
       </c>
       <c r="H208" t="inlineStr">
@@ -7921,6 +8132,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I208" t="inlineStr"/>
     </row>
     <row r="209">
       <c r="A209" t="inlineStr">
@@ -7939,7 +8151,7 @@
         </is>
       </c>
       <c r="D209" t="n">
-        <v>1711435721</v>
+        <v>1714317048</v>
       </c>
       <c r="E209" t="inlineStr">
         <is>
@@ -7949,7 +8161,7 @@
       <c r="F209" t="inlineStr"/>
       <c r="G209" t="inlineStr">
         <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
+          <t>Kitchen.MicrowaveOven001.state: on</t>
         </is>
       </c>
       <c r="H209" t="inlineStr">
@@ -7957,6 +8169,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I209" t="inlineStr"/>
     </row>
     <row r="210">
       <c r="A210" t="inlineStr">
@@ -7975,7 +8188,7 @@
         </is>
       </c>
       <c r="D210" t="n">
-        <v>1711438715</v>
+        <v>1714317239</v>
       </c>
       <c r="E210" t="inlineStr">
         <is>
@@ -7993,6 +8206,7 @@
           <t>physical</t>
         </is>
       </c>
+      <c r="I210" t="inlineStr"/>
     </row>
     <row r="211">
       <c r="A211" t="inlineStr">
@@ -8011,7 +8225,7 @@
         </is>
       </c>
       <c r="D211" t="n">
-        <v>1711441468</v>
+        <v>1714321673</v>
       </c>
       <c r="E211" t="inlineStr">
         <is>
@@ -8029,654 +8243,7 @@
           <t>physical</t>
         </is>
       </c>
-    </row>
-    <row r="212">
-      <c r="A212" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B212" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C212" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D212" t="n">
-        <v>1711444667</v>
-      </c>
-      <c r="E212" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F212" t="inlineStr"/>
-      <c r="G212" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
-        </is>
-      </c>
-      <c r="H212" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="213">
-      <c r="A213" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B213" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C213" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D213" t="n">
-        <v>1711511646</v>
-      </c>
-      <c r="E213" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F213" t="inlineStr"/>
-      <c r="G213" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
-        </is>
-      </c>
-      <c r="H213" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="214">
-      <c r="A214" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B214" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C214" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D214" t="n">
-        <v>1711511828</v>
-      </c>
-      <c r="E214" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F214" t="inlineStr"/>
-      <c r="G214" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
-        </is>
-      </c>
-      <c r="H214" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="215">
-      <c r="A215" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B215" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C215" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D215" t="n">
-        <v>1711514250</v>
-      </c>
-      <c r="E215" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F215" t="inlineStr"/>
-      <c r="G215" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
-        </is>
-      </c>
-      <c r="H215" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="216">
-      <c r="A216" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B216" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C216" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D216" t="n">
-        <v>1711516717</v>
-      </c>
-      <c r="E216" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F216" t="inlineStr"/>
-      <c r="G216" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
-        </is>
-      </c>
-      <c r="H216" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="217">
-      <c r="A217" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B217" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C217" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D217" t="n">
-        <v>1711528013</v>
-      </c>
-      <c r="E217" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F217" t="inlineStr"/>
-      <c r="G217" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
-        </is>
-      </c>
-      <c r="H217" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="218">
-      <c r="A218" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B218" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C218" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D218" t="n">
-        <v>1711528374</v>
-      </c>
-      <c r="E218" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F218" t="inlineStr"/>
-      <c r="G218" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
-        </is>
-      </c>
-      <c r="H218" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="219">
-      <c r="A219" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B219" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C219" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D219" t="n">
-        <v>1711535810</v>
-      </c>
-      <c r="E219" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F219" t="inlineStr"/>
-      <c r="G219" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: on</t>
-        </is>
-      </c>
-      <c r="H219" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="220">
-      <c r="A220" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B220" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C220" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D220" t="n">
-        <v>1711536042</v>
-      </c>
-      <c r="E220" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F220" t="inlineStr"/>
-      <c r="G220" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
-        </is>
-      </c>
-      <c r="H220" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="221">
-      <c r="A221" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B221" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C221" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D221" t="n">
-        <v>1711537920</v>
-      </c>
-      <c r="E221" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F221" t="inlineStr"/>
-      <c r="G221" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
-        </is>
-      </c>
-      <c r="H221" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="222">
-      <c r="A222" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B222" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C222" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D222" t="n">
-        <v>1711540293</v>
-      </c>
-      <c r="E222" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F222" t="inlineStr"/>
-      <c r="G222" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
-        </is>
-      </c>
-      <c r="H222" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="223">
-      <c r="A223" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B223" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C223" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D223" t="n">
-        <v>1711562454</v>
-      </c>
-      <c r="E223" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F223" t="inlineStr"/>
-      <c r="G223" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
-        </is>
-      </c>
-      <c r="H223" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="224">
-      <c r="A224" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B224" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C224" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D224" t="n">
-        <v>1711602609</v>
-      </c>
-      <c r="E224" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F224" t="inlineStr"/>
-      <c r="G224" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
-        </is>
-      </c>
-      <c r="H224" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="225">
-      <c r="A225" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B225" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C225" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D225" t="n">
-        <v>1711605633</v>
-      </c>
-      <c r="E225" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F225" t="inlineStr"/>
-      <c r="G225" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
-        </is>
-      </c>
-      <c r="H225" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="226">
-      <c r="A226" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B226" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C226" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D226" t="n">
-        <v>1711613896</v>
-      </c>
-      <c r="E226" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F226" t="inlineStr"/>
-      <c r="G226" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
-        </is>
-      </c>
-      <c r="H226" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="227">
-      <c r="A227" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B227" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C227" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D227" t="n">
-        <v>1711616061</v>
-      </c>
-      <c r="E227" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F227" t="inlineStr"/>
-      <c r="G227" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
-        </is>
-      </c>
-      <c r="H227" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="228">
-      <c r="A228" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B228" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C228" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D228" t="n">
-        <v>1711618792</v>
-      </c>
-      <c r="E228" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F228" t="inlineStr"/>
-      <c r="G228" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
-        </is>
-      </c>
-      <c r="H228" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
-    </row>
-    <row r="229">
-      <c r="A229" t="inlineStr">
-        <is>
-          <t>Action</t>
-        </is>
-      </c>
-      <c r="B229" t="inlineStr">
-        <is>
-          <t>MicrowaveOven_Operation</t>
-        </is>
-      </c>
-      <c r="C229" t="inlineStr">
-        <is>
-          <t>Kitchen</t>
-        </is>
-      </c>
-      <c r="D229" t="n">
-        <v>1711647459</v>
-      </c>
-      <c r="E229" t="inlineStr">
-        <is>
-          <t>INFO</t>
-        </is>
-      </c>
-      <c r="F229" t="inlineStr"/>
-      <c r="G229" t="inlineStr">
-        <is>
-          <t>Kitchen.MicrowaveOven001.state: off</t>
-        </is>
-      </c>
-      <c r="H229" t="inlineStr">
-        <is>
-          <t>physical</t>
-        </is>
-      </c>
+      <c r="I211" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
